--- a/practice/answers/q012.xlsx
+++ b/practice/answers/q012.xlsx
@@ -2857,21 +2857,21 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>(b) Barley's standard deviation (24.6) is nearly twice canola's (13.3), but that alone does not prove barley is more variable in a meaningful sense: barley yields are also much higher on average (54.6 vs 33.9), and a crop measured on a bigger scale gets a bigger deviation for free.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="46" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>(d) Barley: its CV is 0.45 against canola's 0.39, so relative to its own average, barley varied more across RMs in 2023.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>(e) Relative to typical yields, barley was the more variable crop across Saskatchewan RMs in 2023 -- its yields varied by about 45% of the average, canola's by about 39%.</t>

--- a/practice/answers/q012.xlsx
+++ b/practice/answers/q012.xlsx
@@ -2823,7 +2823,7 @@
         <v/>
       </c>
       <c r="C2" s="2">
-        <f>AVERAGE(Data!$B$2:$B$286)</f>
+        <f>AVERAGE(Data!$B$2:$B$290)</f>
         <v/>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
         <v/>
       </c>
       <c r="C3" s="2">
-        <f>_xlfn.STDEV.S(Data!$B$2:$B$286)</f>
+        <f>_xlfn.STDEV.S(Data!$B$2:$B$290)</f>
         <v/>
       </c>
     </row>

--- a/practice/answers/q012.xlsx
+++ b/practice/answers/q012.xlsx
@@ -1,67 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2843139FB822122AEACDCFDE2F8DE556FA505A33" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE1258B1-EC00-4984-9438-A2C989689625}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Answer" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Canola 2023</t>
+  </si>
+  <si>
+    <t>Barley 2023</t>
+  </si>
+  <si>
+    <t>Canola</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Mean (a)</t>
+  </si>
+  <si>
+    <t>Standard deviation (a)</t>
+  </si>
+  <si>
+    <t>CV (c)</t>
+  </si>
+  <si>
+    <t>(b) Barley's standard deviation (24.6) is nearly twice canola's (13.3), but that alone does not prove barley is more variable in a meaningful sense: barley yields are also much higher on average (54.6 vs 33.9), and a crop measured on a bigger scale gets a bigger deviation for free.</t>
+  </si>
+  <si>
+    <t>(d) Barley: its CV is 0.45 against canola's 0.39, so relative to its own average, barley varied more across RMs in 2023.</t>
+  </si>
+  <si>
+    <t>(e) Relative to typical yields, barley was the more variable crop across Saskatchewan RMs in 2023 -- its yields varied by about 45% of the average, canola's by about 39%.</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+  <si>
+    <t>Part (e)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D2E9"/>
+        <fgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,98 +148,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -456,2327 +469,2318 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B290"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col min="1" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Canola 2023</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Barley 2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="B2">
         <v>53</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:2">
+      <c r="A3">
         <v>34.4</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>50.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:2">
+      <c r="A4">
         <v>31.5</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>62.6</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:2">
+      <c r="A5">
         <v>30.8</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>45</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:2">
+      <c r="A6">
         <v>23.9</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>50</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:2">
+      <c r="A7">
         <v>21</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>54</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:2">
+      <c r="A8">
         <v>21</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>32.6</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:2">
+      <c r="A9">
         <v>20.5</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>22.8</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="B10">
         <v>20.6</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:2">
+      <c r="A11">
         <v>18</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>11.1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:2">
+      <c r="A12">
         <v>30.1</v>
       </c>
-      <c r="B12" t="n">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="B12">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
         <v>30.1</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>73.5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:2">
+      <c r="A14">
         <v>5.5</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>62.1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:2">
+      <c r="A15">
         <v>38.9</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>63.1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:2">
+      <c r="A16">
         <v>37.6</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>63.7</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="B17">
         <v>53.7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:2">
+      <c r="A18">
         <v>35.6</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>45.8</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:2">
+      <c r="A19">
         <v>30.2</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>3.4</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:2">
+      <c r="A20">
         <v>27.4</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>24.9</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:2">
+      <c r="A21">
         <v>24.6</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>29.5</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:2">
+      <c r="A22">
         <v>24.5</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>2.9</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:2">
+      <c r="A23">
         <v>25.8</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>7.5</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:2">
+      <c r="A24">
         <v>18.8</v>
       </c>
-      <c r="B24" t="n">
-        <v>16.9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="B24">
+        <v>16.899999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
         <v>27.4</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>19.2</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:2">
+      <c r="A26">
         <v>11.8</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>28.8</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:2">
+      <c r="A27">
         <v>10.8</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>40.1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:2">
+      <c r="A28">
         <v>13.4</v>
       </c>
-      <c r="B28" t="n">
-        <v>74.90000000000001</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="B28">
+        <v>74.900000000000006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
         <v>12.7</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>76.5</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:2">
+      <c r="A30">
         <v>19</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>58.1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:2">
+      <c r="A31">
         <v>42.8</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>51.7</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:2">
+      <c r="A32">
         <v>42</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>48.7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:2">
+      <c r="A33">
         <v>35.9</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>54.1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:2">
+      <c r="A34">
         <v>28.2</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>42.6</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:2">
+      <c r="A35">
         <v>24.9</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>20.2</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:2">
+      <c r="A36">
         <v>29.8</v>
       </c>
-      <c r="B36" t="n">
-        <v>34.7</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="B36">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
         <v>26.3</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>24.9</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:2">
+      <c r="A38">
         <v>21.5</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>43.5</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:2">
+      <c r="A39">
         <v>27.3</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>36.9</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:2">
+      <c r="A40">
         <v>17.5</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>15.3</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="B41" t="n">
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="B41">
         <v>7.9</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:2">
+      <c r="A42">
         <v>15.9</v>
       </c>
-      <c r="B42" t="n">
-        <v>18.4</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="B42">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
         <v>12.3</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>9.6</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:2">
+      <c r="A44">
         <v>12.2</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>18.2</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:2">
+      <c r="A45">
         <v>13.8</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>27.7</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="B46" t="n">
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="B46">
         <v>74.5</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:2">
+      <c r="A47">
         <v>14.2</v>
       </c>
-      <c r="B47" t="n">
-        <v>77.40000000000001</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="B47">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
         <v>16.7</v>
       </c>
-      <c r="B48" t="n">
-        <v>66.90000000000001</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="B48">
+        <v>66.900000000000006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
         <v>43</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>59.9</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:2">
+      <c r="A50">
         <v>43.1</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>44.7</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:2">
+      <c r="A51">
         <v>43.2</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>42.8</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:2">
+      <c r="A52">
         <v>34</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>48.1</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:2">
+      <c r="A53">
         <v>29.2</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>76.7</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:2">
+      <c r="A54">
         <v>29.2</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>29.4</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:2">
+      <c r="A55">
         <v>31.6</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>56.6</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:2">
+      <c r="A56">
         <v>32.1</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>15.4</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:2">
+      <c r="A57">
         <v>31.9</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>44.8</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:2">
+      <c r="A58">
         <v>31.1</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>22.5</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:2">
+      <c r="A59">
         <v>24.9</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>28.9</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:2">
+      <c r="A60">
         <v>20.9</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>30.5</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:2">
+      <c r="A61">
         <v>16.7</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>26</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:2">
+      <c r="A62">
         <v>22.7</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>25.6</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="B63" t="n">
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="B63">
         <v>17.2</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:2">
+      <c r="A64">
         <v>17</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>25.7</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:2">
+      <c r="A65">
         <v>15.3</v>
       </c>
-      <c r="B65" t="n">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="B65">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
         <v>11.4</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>32.9</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:2">
+      <c r="A67">
         <v>14.7</v>
       </c>
-      <c r="B67" t="n">
-        <v>67.09999999999999</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="B67">
+        <v>67.099999999999994</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
         <v>24.1</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>49.8</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="B69" t="n">
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="B69">
         <v>70.5</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:2">
+      <c r="A70">
         <v>49.4</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>53.7</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:2">
+      <c r="A71">
         <v>35.9</v>
       </c>
-      <c r="B71" t="n">
-        <v>67.59999999999999</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="B72" t="n">
+      <c r="B71">
+        <v>67.599999999999994</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="B72">
         <v>72.5</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:2">
+      <c r="A73">
         <v>35.5</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>68.3</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:2">
+      <c r="A74">
         <v>39.6</v>
       </c>
-      <c r="B74" t="n">
-        <v>83.09999999999999</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="B74">
+        <v>83.1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
         <v>40.9</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>76.5</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="B76" t="n">
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="B76">
         <v>49.9</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:2">
+      <c r="A77">
         <v>42.5</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>55.7</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:2">
+      <c r="A78">
         <v>42.6</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>29.8</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="B79" t="n">
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>39.299999999999997</v>
+      </c>
+      <c r="B79">
         <v>3.8</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:2">
+      <c r="A80">
         <v>31.4</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>27.9</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:2">
+      <c r="A81">
         <v>21.8</v>
       </c>
-      <c r="B81" t="n">
-        <v>33.8</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
+      <c r="B81">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
         <v>22.4</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>44.4</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:2">
+      <c r="A83">
         <v>22.4</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>31.6</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:2">
+      <c r="A84">
         <v>22.6</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>28.7</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:2">
+      <c r="A85">
         <v>20.2</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>10.3</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:2">
+      <c r="A86">
         <v>19.7</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>7.7</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:2">
+      <c r="A87">
         <v>18.2</v>
       </c>
-      <c r="B87" t="n">
-        <v>9.800000000000001</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
+      <c r="B87">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
         <v>6.9</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>51.4</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:2">
+      <c r="A89">
         <v>3.4</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>67</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:2">
+      <c r="A90">
         <v>4.8</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>84</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:2">
+      <c r="A91">
         <v>41.9</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>71.7</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="B92" t="n">
-        <v>77.40000000000001</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="B92">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
         <v>37.4</v>
       </c>
-      <c r="B93" t="n">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
+      <c r="B93">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
         <v>35</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>76.3</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:2">
+      <c r="A95">
         <v>42.8</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>79.3</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:2">
+      <c r="A96">
         <v>45.8</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>69.7</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:2">
+      <c r="A97">
         <v>47.8</v>
       </c>
-      <c r="B97" t="n">
-        <v>77.40000000000001</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
+      <c r="B97">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
         <v>44.9</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>53.6</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:2">
+      <c r="A99">
         <v>47.4</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>35.1</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:2">
+      <c r="A100">
         <v>42.4</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>24.8</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="B101" t="n">
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>36.299999999999997</v>
+      </c>
+      <c r="B101">
         <v>11.3</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="B102" t="n">
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>36.799999999999997</v>
+      </c>
+      <c r="B102">
         <v>22.9</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:2">
+      <c r="A103">
         <v>24.3</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>27.4</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:2">
+      <c r="A104">
         <v>20.2</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>26.5</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:2">
+      <c r="A105">
         <v>19.8</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>18.7</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
+    <row r="106" spans="1:2">
+      <c r="A106">
         <v>15.8</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>11.8</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="B107" t="n">
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="B107">
         <v>4.5</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:2">
+      <c r="A108">
         <v>9.5</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>88</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:2">
+      <c r="A109">
         <v>10.4</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>61.9</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:2">
+      <c r="A110">
         <v>40.1</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>63.4</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:2">
+      <c r="A111">
         <v>39</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>74.3</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:2">
+      <c r="A112">
         <v>36.9</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>86.3</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:2">
+      <c r="A113">
         <v>43.8</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>73.3</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:2">
+      <c r="A114">
         <v>46.7</v>
       </c>
-      <c r="B114" t="n">
-        <v>72.59999999999999</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
+      <c r="B114">
+        <v>72.599999999999994</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
         <v>48.8</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>44.6</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
+    <row r="116" spans="1:2">
+      <c r="A116">
         <v>40.1</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>41.6</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="n">
+    <row r="117" spans="1:2">
+      <c r="A117">
         <v>25</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>22.1</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="118" spans="1:2">
+      <c r="A118">
         <v>29.5</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>26.5</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:2">
+      <c r="A119">
         <v>19.5</v>
       </c>
-      <c r="B119" t="n">
-        <v>77.59999999999999</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
+      <c r="B119">
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
         <v>18.3</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>70.5</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="121" spans="1:2">
+      <c r="A121">
         <v>46.7</v>
       </c>
-      <c r="B121" t="n">
-        <v>74.40000000000001</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
+      <c r="B121">
+        <v>74.400000000000006</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
         <v>43.1</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>73.7</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:2">
+      <c r="A123">
         <v>43.5</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>62.6</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:2">
+      <c r="A124">
         <v>44</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>78.8</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="B125" t="n">
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="B125">
         <v>70.5</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="B126" t="n">
-        <v>67.40000000000001</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>40.299999999999997</v>
+      </c>
+      <c r="B126">
+        <v>67.400000000000006</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
         <v>43.5</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>64.3</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="B128" t="n">
-        <v>78.40000000000001</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="B128">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
         <v>35.1</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129">
         <v>46.7</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="n">
+    <row r="130" spans="1:2">
+      <c r="A130">
         <v>26.4</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130">
         <v>27.8</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
+    <row r="131" spans="1:2">
+      <c r="A131">
         <v>25.2</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131">
         <v>47</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="132" spans="1:2">
+      <c r="A132">
         <v>16.2</v>
       </c>
-      <c r="B132" t="n">
+      <c r="B132">
         <v>15.3</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="n">
+    <row r="133" spans="1:2">
+      <c r="A133">
         <v>25.4</v>
       </c>
-      <c r="B133" t="n">
+      <c r="B133">
         <v>28.8</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="n">
+    <row r="134" spans="1:2">
+      <c r="A134">
         <v>13.9</v>
       </c>
-      <c r="B134" t="n">
+      <c r="B134">
         <v>16.2</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
+    <row r="135" spans="1:2">
+      <c r="A135">
         <v>15.9</v>
       </c>
-      <c r="B135" t="n">
+      <c r="B135">
         <v>20.5</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="n">
+    <row r="136" spans="1:2">
+      <c r="A136">
         <v>13</v>
       </c>
-      <c r="B136" t="n">
+      <c r="B136">
         <v>15.8</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="n">
+    <row r="137" spans="1:2">
+      <c r="A137">
         <v>7.6</v>
       </c>
-      <c r="B137" t="n">
+      <c r="B137">
         <v>12.6</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="n">
+    <row r="138" spans="1:2">
+      <c r="A138">
         <v>11.6</v>
       </c>
-      <c r="B138" t="n">
+      <c r="B138">
         <v>10.3</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="B139" t="n">
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="B139">
         <v>62.1</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
+    <row r="140" spans="1:2">
+      <c r="A140">
         <v>14.3</v>
       </c>
-      <c r="B140" t="n">
-        <v>91.40000000000001</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="B141" t="n">
+      <c r="B140">
+        <v>91.4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="B141">
         <v>66.5</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="B142" t="n">
-        <v>71.90000000000001</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="B142">
+        <v>71.900000000000006</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
         <v>43.9</v>
       </c>
-      <c r="B143" t="n">
+      <c r="B143">
         <v>72</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="144" spans="1:2">
+      <c r="A144">
         <v>40.6</v>
       </c>
-      <c r="B144" t="n">
-        <v>78.59999999999999</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
+      <c r="B144">
+        <v>78.599999999999994</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
         <v>42.6</v>
       </c>
-      <c r="B145" t="n">
-        <v>71.59999999999999</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
+      <c r="B145">
+        <v>71.599999999999994</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
         <v>45</v>
       </c>
-      <c r="B146" t="n">
+      <c r="B146">
         <v>50.2</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="147" spans="1:2">
+      <c r="A147">
         <v>38.1</v>
       </c>
-      <c r="B147" t="n">
+      <c r="B147">
         <v>45.9</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="148" spans="1:2">
+      <c r="A148">
         <v>30.2</v>
       </c>
-      <c r="B148" t="n">
+      <c r="B148">
         <v>52</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="149" spans="1:2">
+      <c r="A149">
         <v>27.9</v>
       </c>
-      <c r="B149" t="n">
+      <c r="B149">
         <v>26.7</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="150" spans="1:2">
+      <c r="A150">
         <v>29</v>
       </c>
-      <c r="B150" t="n">
+      <c r="B150">
         <v>29.7</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="151" spans="1:2">
+      <c r="A151">
         <v>17.8</v>
       </c>
-      <c r="B151" t="n">
+      <c r="B151">
         <v>28</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="n">
+    <row r="152" spans="1:2">
+      <c r="A152">
         <v>14.9</v>
       </c>
-      <c r="B152" t="n">
+      <c r="B152">
         <v>20.8</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="n">
+    <row r="153" spans="1:2">
+      <c r="A153">
         <v>19.7</v>
       </c>
-      <c r="B153" t="n">
+      <c r="B153">
         <v>18.5</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="n">
+    <row r="154" spans="1:2">
+      <c r="A154">
         <v>11.5</v>
       </c>
-      <c r="B154" t="n">
-        <v>34.7</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
+      <c r="B154">
+        <v>34.700000000000003</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
         <v>13.2</v>
       </c>
-      <c r="B155" t="n">
+      <c r="B155">
         <v>30.7</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="n">
+    <row r="156" spans="1:2">
+      <c r="A156">
         <v>17</v>
       </c>
-      <c r="B156" t="n">
+      <c r="B156">
         <v>23.4</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="B157" t="n">
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="B157">
         <v>69.7</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="n">
+    <row r="158" spans="1:2">
+      <c r="A158">
         <v>18.5</v>
       </c>
-      <c r="B158" t="n">
-        <v>68.90000000000001</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
+      <c r="B158">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
         <v>48.2</v>
       </c>
-      <c r="B159" t="n">
+      <c r="B159">
         <v>84.5</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="160" spans="1:2">
+      <c r="A160">
         <v>47.9</v>
       </c>
-      <c r="B160" t="n">
-        <v>82.40000000000001</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
+      <c r="B160">
+        <v>82.4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
         <v>51.5</v>
       </c>
-      <c r="B161" t="n">
-        <v>83.40000000000001</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
+      <c r="B161">
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
         <v>42.2</v>
       </c>
-      <c r="B162" t="n">
+      <c r="B162">
         <v>57.9</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="n">
+    <row r="163" spans="1:2">
+      <c r="A163">
         <v>48.6</v>
       </c>
-      <c r="B163" t="n">
-        <v>64.90000000000001</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="B164" t="n">
+      <c r="B163">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="B164">
         <v>68.3</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="n">
+    <row r="165" spans="1:2">
+      <c r="A165">
         <v>42.8</v>
       </c>
-      <c r="B165" t="n">
+      <c r="B165">
         <v>52.5</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="n">
+    <row r="166" spans="1:2">
+      <c r="A166">
         <v>34.4</v>
       </c>
-      <c r="B166" t="n">
+      <c r="B166">
         <v>24.7</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="n">
+    <row r="167" spans="1:2">
+      <c r="A167">
         <v>27.7</v>
       </c>
-      <c r="B167" t="n">
+      <c r="B167">
         <v>20.6</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="n">
+    <row r="168" spans="1:2">
+      <c r="A168">
         <v>16.5</v>
       </c>
-      <c r="B168" t="n">
+      <c r="B168">
         <v>24.1</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="n">
+    <row r="169" spans="1:2">
+      <c r="A169">
         <v>13.7</v>
       </c>
-      <c r="B169" t="n">
+      <c r="B169">
         <v>30.1</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="B170" t="n">
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="B170">
         <v>43.1</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="n">
+    <row r="171" spans="1:2">
+      <c r="A171">
         <v>21.2</v>
       </c>
-      <c r="B171" t="n">
+      <c r="B171">
         <v>24.7</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" t="n">
+    <row r="172" spans="1:2">
+      <c r="A172">
         <v>20.2</v>
       </c>
-      <c r="B172" t="n">
+      <c r="B172">
         <v>36.5</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="n">
+    <row r="173" spans="1:2">
+      <c r="A173">
         <v>18.5</v>
       </c>
-      <c r="B173" t="n">
+      <c r="B173">
         <v>36.1</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="n">
+    <row r="174" spans="1:2">
+      <c r="A174">
         <v>26.8</v>
       </c>
-      <c r="B174" t="n">
+      <c r="B174">
         <v>93.7</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="n">
+    <row r="175" spans="1:2">
+      <c r="A175">
         <v>22.5</v>
       </c>
-      <c r="B175" t="n">
+      <c r="B175">
         <v>94.3</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="n">
+    <row r="176" spans="1:2">
+      <c r="A176">
         <v>48.5</v>
       </c>
-      <c r="B176" t="n">
-        <v>92.40000000000001</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
+      <c r="B176">
+        <v>92.4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
         <v>60.1</v>
       </c>
-      <c r="B177" t="n">
+      <c r="B177">
         <v>67.7</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="n">
+    <row r="178" spans="1:2">
+      <c r="A178">
         <v>57</v>
       </c>
-      <c r="B178" t="n">
+      <c r="B178">
         <v>80.3</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="n">
+    <row r="179" spans="1:2">
+      <c r="A179">
         <v>53.9</v>
       </c>
-      <c r="B179" t="n">
+      <c r="B179">
         <v>86.5</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="n">
+    <row r="180" spans="1:2">
+      <c r="A180">
         <v>44.5</v>
       </c>
-      <c r="B180" t="n">
-        <v>69.59999999999999</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
+      <c r="B180">
+        <v>69.599999999999994</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
         <v>47.3</v>
       </c>
-      <c r="B181" t="n">
+      <c r="B181">
         <v>60.6</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="n">
+    <row r="182" spans="1:2">
+      <c r="A182">
         <v>48.9</v>
       </c>
-      <c r="B182" t="n">
+      <c r="B182">
         <v>34.1</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="n">
+    <row r="183" spans="1:2">
+      <c r="A183">
         <v>43.7</v>
       </c>
-      <c r="B183" t="n">
+      <c r="B183">
         <v>31.9</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="n">
+    <row r="184" spans="1:2">
+      <c r="A184">
         <v>31.4</v>
       </c>
-      <c r="B184" t="n">
+      <c r="B184">
         <v>13.2</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="n">
+    <row r="185" spans="1:2">
+      <c r="A185">
         <v>26</v>
       </c>
-      <c r="B185" t="n">
+      <c r="B185">
         <v>56.9</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="n">
+    <row r="186" spans="1:2">
+      <c r="A186">
         <v>26.4</v>
       </c>
-      <c r="B186" t="n">
+      <c r="B186">
         <v>53.1</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="n">
+    <row r="187" spans="1:2">
+      <c r="A187">
         <v>21.8</v>
       </c>
-      <c r="B187" t="n">
-        <v>32.3</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
+      <c r="B187">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
         <v>25.5</v>
       </c>
-      <c r="B188" t="n">
+      <c r="B188">
         <v>41.8</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="n">
+    <row r="189" spans="1:2">
+      <c r="A189">
         <v>26.4</v>
       </c>
-      <c r="B189" t="n">
+      <c r="B189">
         <v>42.1</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="n">
+    <row r="190" spans="1:2">
+      <c r="A190">
         <v>24</v>
       </c>
-      <c r="B190" t="n">
+      <c r="B190">
         <v>37.9</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="n">
+    <row r="191" spans="1:2">
+      <c r="A191">
         <v>26.3</v>
       </c>
-      <c r="B191" t="n">
+      <c r="B191">
         <v>7.7</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="n">
+    <row r="192" spans="1:2">
+      <c r="A192">
         <v>25.3</v>
       </c>
-      <c r="B192" t="n">
+      <c r="B192">
         <v>72.2</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="n">
+    <row r="193" spans="1:2">
+      <c r="A193">
         <v>29.8</v>
       </c>
-      <c r="B193" t="n">
+      <c r="B193">
         <v>95.8</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="n">
+    <row r="194" spans="1:2">
+      <c r="A194">
         <v>22.7</v>
       </c>
-      <c r="B194" t="n">
+      <c r="B194">
         <v>86.2</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
+    <row r="195" spans="1:2">
+      <c r="A195">
         <v>43.7</v>
       </c>
-      <c r="B195" t="n">
+      <c r="B195">
         <v>92</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="n">
+    <row r="196" spans="1:2">
+      <c r="A196">
         <v>58.6</v>
       </c>
-      <c r="B196" t="n">
+      <c r="B196">
         <v>91.8</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="n">
+    <row r="197" spans="1:2">
+      <c r="A197">
         <v>56.6</v>
       </c>
-      <c r="B197" t="n">
-        <v>86.90000000000001</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
+      <c r="B197">
+        <v>86.9</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
         <v>55.9</v>
       </c>
-      <c r="B198" t="n">
+      <c r="B198">
         <v>94.7</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="n">
+    <row r="199" spans="1:2">
+      <c r="A199">
         <v>55.3</v>
       </c>
-      <c r="B199" t="n">
+      <c r="B199">
         <v>72</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="n">
+    <row r="200" spans="1:2">
+      <c r="A200">
         <v>52</v>
       </c>
-      <c r="B200" t="n">
+      <c r="B200">
         <v>82.5</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="n">
+    <row r="201" spans="1:2">
+      <c r="A201">
         <v>54.1</v>
       </c>
-      <c r="B201" t="n">
+      <c r="B201">
         <v>59.3</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="n">
+    <row r="202" spans="1:2">
+      <c r="A202">
         <v>50.4</v>
       </c>
-      <c r="B202" t="n">
+      <c r="B202">
         <v>57</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="n">
+    <row r="203" spans="1:2">
+      <c r="A203">
         <v>50.6</v>
       </c>
-      <c r="B203" t="n">
+      <c r="B203">
         <v>43.3</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="n">
+    <row r="204" spans="1:2">
+      <c r="A204">
         <v>40.5</v>
       </c>
-      <c r="B204" t="n">
+      <c r="B204">
         <v>40.9</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="B205" t="n">
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="B205">
         <v>39.6</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="206" spans="1:2">
+      <c r="A206">
         <v>28.5</v>
       </c>
-      <c r="B206" t="n">
-        <v>34.8</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
+      <c r="B206">
+        <v>34.799999999999997</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
         <v>28.4</v>
       </c>
-      <c r="B207" t="n">
+      <c r="B207">
         <v>48.9</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="n">
+    <row r="208" spans="1:2">
+      <c r="A208">
         <v>29.2</v>
       </c>
-      <c r="B208" t="n">
+      <c r="B208">
         <v>35.5</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="n">
+    <row r="209" spans="1:2">
+      <c r="A209">
         <v>25</v>
       </c>
-      <c r="B209" t="n">
+      <c r="B209">
         <v>44.4</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="n">
+    <row r="210" spans="1:2">
+      <c r="A210">
         <v>28.1</v>
       </c>
-      <c r="B210" t="n">
+      <c r="B210">
         <v>51.2</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="n">
+    <row r="211" spans="1:2">
+      <c r="A211">
         <v>32.6</v>
       </c>
-      <c r="B211" t="n">
+      <c r="B211">
         <v>52.3</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="n">
+    <row r="212" spans="1:2">
+      <c r="A212">
         <v>25.2</v>
       </c>
-      <c r="B212" t="n">
-        <v>84.59999999999999</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
+      <c r="B212">
+        <v>84.6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
         <v>30.3</v>
       </c>
-      <c r="B213" t="n">
+      <c r="B213">
         <v>90.8</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="n">
+    <row r="214" spans="1:2">
+      <c r="A214">
         <v>35</v>
       </c>
-      <c r="B214" t="n">
-        <v>96.90000000000001</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
+      <c r="B214">
+        <v>96.9</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
         <v>48.6</v>
       </c>
-      <c r="B215" t="n">
+      <c r="B215">
         <v>86.5</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="n">
+    <row r="216" spans="1:2">
+      <c r="A216">
         <v>56.6</v>
       </c>
-      <c r="B216" t="n">
+      <c r="B216">
         <v>87.5</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="n">
+    <row r="217" spans="1:2">
+      <c r="A217">
         <v>58.3</v>
       </c>
-      <c r="B217" t="n">
+      <c r="B217">
         <v>73.3</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="n">
+    <row r="218" spans="1:2">
+      <c r="A218">
         <v>55</v>
       </c>
-      <c r="B218" t="n">
+      <c r="B218">
         <v>55</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="n">
+    <row r="219" spans="1:2">
+      <c r="A219">
         <v>50.6</v>
       </c>
-      <c r="B219" t="n">
+      <c r="B219">
         <v>59.2</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="n">
+    <row r="220" spans="1:2">
+      <c r="A220">
         <v>45.1</v>
       </c>
-      <c r="B220" t="n">
+      <c r="B220">
         <v>42.2</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="B221" t="n">
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="B221">
         <v>63.9</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="B222" t="n">
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="B222">
         <v>51.7</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="n">
+    <row r="223" spans="1:2">
+      <c r="A223">
         <v>21.6</v>
       </c>
-      <c r="B223" t="n">
+      <c r="B223">
         <v>75.2</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="n">
+    <row r="224" spans="1:2">
+      <c r="A224">
         <v>32.9</v>
       </c>
-      <c r="B224" t="n">
+      <c r="B224">
         <v>61.3</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="n">
+    <row r="225" spans="1:2">
+      <c r="A225">
         <v>34.5</v>
       </c>
-      <c r="B225" t="n">
+      <c r="B225">
         <v>57.5</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" t="n">
+    <row r="226" spans="1:2">
+      <c r="A226">
         <v>38.6</v>
       </c>
-      <c r="B226" t="n">
+      <c r="B226">
         <v>60.8</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="n">
+    <row r="227" spans="1:2">
+      <c r="A227">
         <v>35.5</v>
       </c>
-      <c r="B227" t="n">
+      <c r="B227">
         <v>64.7</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="n">
+    <row r="228" spans="1:2">
+      <c r="A228">
         <v>32</v>
       </c>
-      <c r="B228" t="n">
+      <c r="B228">
         <v>84</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="n">
+    <row r="229" spans="1:2">
+      <c r="A229">
         <v>36.4</v>
       </c>
-      <c r="B229" t="n">
-        <v>67.40000000000001</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="B229">
+        <v>67.400000000000006</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
         <v>41.1</v>
       </c>
-      <c r="B230" t="n">
+      <c r="B230">
         <v>85.8</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" t="n">
+    <row r="231" spans="1:2">
+      <c r="A231">
         <v>53.9</v>
       </c>
-      <c r="B231" t="n">
-        <v>79.90000000000001</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
+      <c r="B231">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
         <v>47</v>
       </c>
-      <c r="B232" t="n">
-        <v>83.90000000000001</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="B232">
+        <v>83.9</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
         <v>53.7</v>
       </c>
-      <c r="B233" t="n">
+      <c r="B233">
         <v>73</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="n">
+    <row r="234" spans="1:2">
+      <c r="A234">
         <v>51.8</v>
       </c>
-      <c r="B234" t="n">
+      <c r="B234">
         <v>62.9</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="n">
+    <row r="235" spans="1:2">
+      <c r="A235">
         <v>47.8</v>
       </c>
-      <c r="B235" t="n">
+      <c r="B235">
         <v>74</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="236" spans="1:2">
+      <c r="A236">
         <v>44.9</v>
       </c>
-      <c r="B236" t="n">
-        <v>78.59999999999999</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="B237" t="n">
+      <c r="B236">
+        <v>78.599999999999994</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="B237">
         <v>46.9</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="n">
+    <row r="238" spans="1:2">
+      <c r="A238">
         <v>46.7</v>
       </c>
-      <c r="B238" t="n">
+      <c r="B238">
         <v>48.2</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="n">
+    <row r="239" spans="1:2">
+      <c r="A239">
         <v>46.3</v>
       </c>
-      <c r="B239" t="n">
+      <c r="B239">
         <v>71.3</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="n">
+    <row r="240" spans="1:2">
+      <c r="A240">
         <v>32.1</v>
       </c>
-      <c r="B240" t="n">
+      <c r="B240">
         <v>62.3</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="n">
+    <row r="241" spans="1:2">
+      <c r="A241">
         <v>30.8</v>
       </c>
-      <c r="B241" t="n">
+      <c r="B241">
         <v>61.9</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="B242" t="n">
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="B242">
         <v>73</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="n">
+    <row r="243" spans="1:2">
+      <c r="A243">
         <v>42.1</v>
       </c>
-      <c r="B243" t="n">
+      <c r="B243">
         <v>74</v>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="B244" t="n">
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="B244">
         <v>70</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" t="n">
+    <row r="245" spans="1:2">
+      <c r="A245">
         <v>49.7</v>
       </c>
-      <c r="B245" t="n">
+      <c r="B245">
         <v>69.3</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="n">
+    <row r="246" spans="1:2">
+      <c r="A246">
         <v>47.7</v>
       </c>
-      <c r="B246" t="n">
+      <c r="B246">
         <v>73.3</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="n">
+    <row r="247" spans="1:2">
+      <c r="A247">
         <v>45.6</v>
       </c>
-      <c r="B247" t="n">
-        <v>69.09999999999999</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
+      <c r="B247">
+        <v>69.099999999999994</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
         <v>41.4</v>
       </c>
-      <c r="B248" t="n">
+      <c r="B248">
         <v>62.4</v>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" t="n">
+    <row r="249" spans="1:2">
+      <c r="A249">
         <v>45.2</v>
       </c>
-      <c r="B249" t="n">
+      <c r="B249">
         <v>59.9</v>
       </c>
     </row>
-    <row r="250">
-      <c r="A250" t="n">
+    <row r="250" spans="1:2">
+      <c r="A250">
         <v>46.1</v>
       </c>
-      <c r="B250" t="n">
+      <c r="B250">
         <v>54.1</v>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" t="n">
+    <row r="251" spans="1:2">
+      <c r="A251">
         <v>50.4</v>
       </c>
-      <c r="B251" t="n">
+      <c r="B251">
         <v>78</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="B252" t="n">
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="B252">
         <v>82</v>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" t="n">
+    <row r="253" spans="1:2">
+      <c r="A253">
         <v>31.7</v>
       </c>
-      <c r="B253" t="n">
-        <v>76.59999999999999</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="B254" t="n">
+      <c r="B253">
+        <v>76.599999999999994</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="B254">
         <v>67.2</v>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="B255" t="n">
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="B255">
         <v>61.1</v>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" t="n">
+    <row r="256" spans="1:2">
+      <c r="A256">
         <v>48.7</v>
       </c>
-      <c r="B256" t="n">
+      <c r="B256">
         <v>64.2</v>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" t="n">
+    <row r="257" spans="1:2">
+      <c r="A257">
         <v>42.1</v>
       </c>
-      <c r="B257" t="n">
+      <c r="B257">
         <v>70.8</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="n">
+    <row r="258" spans="1:2">
+      <c r="A258">
         <v>43.1</v>
       </c>
-      <c r="B258" t="n">
+      <c r="B258">
         <v>67.3</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="B259" t="n">
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>39.799999999999997</v>
+      </c>
+      <c r="B259">
         <v>75.5</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="n">
+    <row r="260" spans="1:2">
+      <c r="A260">
         <v>44.3</v>
       </c>
-      <c r="B260" t="n">
+      <c r="B260">
         <v>70.8</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="n">
+    <row r="261" spans="1:2">
+      <c r="A261">
         <v>51.5</v>
       </c>
-      <c r="B261" t="n">
+      <c r="B261">
         <v>75.5</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="n">
+    <row r="262" spans="1:2">
+      <c r="A262">
         <v>45.3</v>
       </c>
-      <c r="B262" t="n">
+      <c r="B262">
         <v>63.5</v>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" t="n">
+    <row r="263" spans="1:2">
+      <c r="A263">
         <v>46</v>
       </c>
-      <c r="B263" t="n">
-        <v>88.59999999999999</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
+      <c r="B263">
+        <v>88.6</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
         <v>49.9</v>
       </c>
-      <c r="B264" t="n">
-        <v>80.40000000000001</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
+      <c r="B264">
+        <v>80.400000000000006</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
         <v>42.6</v>
       </c>
-      <c r="B265" t="n">
-        <v>69.90000000000001</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
+      <c r="B265">
+        <v>69.900000000000006</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
         <v>56.5</v>
       </c>
-      <c r="B266" t="n">
+      <c r="B266">
         <v>77.3</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" t="n">
+    <row r="267" spans="1:2">
+      <c r="A267">
         <v>41.4</v>
       </c>
-      <c r="B267" t="n">
+      <c r="B267">
         <v>60.4</v>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" t="n">
+    <row r="268" spans="1:2">
+      <c r="A268">
         <v>35.6</v>
       </c>
-      <c r="B268" t="n">
-        <v>84.09999999999999</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
+      <c r="B268">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
         <v>45.2</v>
       </c>
-      <c r="B269" t="n">
+      <c r="B269">
         <v>83.2</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="n">
+    <row r="270" spans="1:2">
+      <c r="A270">
         <v>49.3</v>
       </c>
-      <c r="B270" t="n">
+      <c r="B270">
         <v>81.7</v>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" t="n">
+    <row r="271" spans="1:2">
+      <c r="A271">
         <v>46.8</v>
       </c>
-      <c r="B271" t="n">
-        <v>79.09999999999999</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
+      <c r="B271">
+        <v>79.099999999999994</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
         <v>46.7</v>
       </c>
-      <c r="B272" t="n">
+      <c r="B272">
         <v>68.3</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="n">
+    <row r="273" spans="1:2">
+      <c r="A273">
         <v>51.8</v>
       </c>
-      <c r="B273" t="n">
-        <v>75.40000000000001</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
+      <c r="B273">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
         <v>50.2</v>
       </c>
-      <c r="B274" t="n">
+      <c r="B274">
         <v>77.5</v>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" t="n">
+    <row r="275" spans="1:2">
+      <c r="A275">
         <v>49.6</v>
       </c>
-      <c r="B275" t="n">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
+      <c r="B275">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
         <v>55.3</v>
       </c>
-      <c r="B276" t="n">
+      <c r="B276">
         <v>97.2</v>
       </c>
     </row>
-    <row r="277">
-      <c r="A277" t="n">
+    <row r="277" spans="1:2">
+      <c r="A277">
         <v>51.3</v>
       </c>
-      <c r="B277" t="n">
-        <v>88.59999999999999</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
+      <c r="B277">
+        <v>88.6</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
         <v>56</v>
       </c>
-      <c r="B278" t="n">
-        <v>88.59999999999999</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
+      <c r="B278">
+        <v>88.6</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
         <v>53.6</v>
       </c>
-      <c r="B279" t="n">
+      <c r="B279">
         <v>73.7</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" t="n">
+    <row r="280" spans="1:2">
+      <c r="A280">
         <v>51.8</v>
       </c>
-      <c r="B280" t="n">
-        <v>81.90000000000001</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
+      <c r="B280">
+        <v>81.900000000000006</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
         <v>50.4</v>
       </c>
-      <c r="B281" t="n">
+      <c r="B281">
         <v>72.7</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="n">
+    <row r="282" spans="1:2">
+      <c r="A282">
         <v>45.6</v>
       </c>
-      <c r="B282" t="n">
+      <c r="B282">
         <v>76</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="n">
+    <row r="283" spans="1:2">
+      <c r="A283">
         <v>49.9</v>
       </c>
-      <c r="B283" t="n">
+      <c r="B283">
         <v>58.7</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="n">
+    <row r="284" spans="1:2">
+      <c r="A284">
         <v>48.4</v>
       </c>
-      <c r="B284" t="n">
+      <c r="B284">
         <v>99</v>
       </c>
     </row>
-    <row r="285">
-      <c r="A285" t="n">
+    <row r="285" spans="1:2">
+      <c r="A285">
         <v>42.2</v>
       </c>
-      <c r="B285" t="n">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
+      <c r="B285">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
         <v>51.1</v>
       </c>
-      <c r="B286" t="n">
+      <c r="B286">
         <v>74.8</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="n">
+    <row r="287" spans="1:2">
+      <c r="A287">
         <v>54.2</v>
       </c>
     </row>
-    <row r="288">
-      <c r="A288" t="n">
+    <row r="288" spans="1:2">
+      <c r="A288">
         <v>50.8</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="n">
+    <row r="289" spans="1:1">
+      <c r="A289">
         <v>46.6</v>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" t="n">
+    <row r="290" spans="1:1">
+      <c r="A290">
         <v>45.9</v>
       </c>
     </row>
@@ -2786,138 +2790,116 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Canola</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Barley</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Mean (a)</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2">
         <f>AVERAGE(Data!$A$2:$A$290)</f>
-        <v/>
+        <v>33.880968858131482</v>
       </c>
       <c r="C2" s="2">
         <f>AVERAGE(Data!$B$2:$B$290)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Standard deviation (a)</t>
-        </is>
+        <v>54.563859649122804</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B3" s="2">
         <f>_xlfn.STDEV.S(Data!$A$2:$A$290)</f>
-        <v/>
+        <v>13.334641254694027</v>
       </c>
       <c r="C3" s="2">
         <f>_xlfn.STDEV.S(Data!$B$2:$B$290)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>CV (c)</t>
-        </is>
+        <v>24.60321874012828</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="3">
         <f>B3/B2</f>
-        <v/>
+        <v>0.3935731977007409</v>
       </c>
       <c r="C4" s="3">
         <f>C3/C2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>(b) Barley's standard deviation (24.6) is nearly twice canola's (13.3), but that alone does not prove barley is more variable in a meaningful sense: barley yields are also much higher on average (54.6 vs 33.9), and a crop measured on a bigger scale gets a bigger deviation for free.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>(d) Barley: its CV is 0.45 against canola's 0.39, so relative to its own average, barley varied more across RMs in 2023.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>(e) Relative to typical yields, barley was the more variable crop across Saskatchewan RMs in 2023 -- its yields varied by about 45% of the average, canola's by about 39%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>Part (e)</t>
-        </is>
+        <v>0.45090686213074399</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="63.95" customHeight="1">
+      <c r="A6" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+    </row>
+    <row r="7" spans="1:5" ht="63.95" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+    </row>
+    <row r="8" spans="1:5" ht="63.95" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
